--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532196</v>
+        <v>119532121</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554849</v>
+        <v>555245</v>
       </c>
       <c r="R6" t="n">
-        <v>6954924</v>
+        <v>6955133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119532121</v>
+        <v>119532196</v>
       </c>
       <c r="B7" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555245</v>
+        <v>554849</v>
       </c>
       <c r="R7" t="n">
-        <v>6955133</v>
+        <v>6954924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119532123</v>
+        <v>119532166</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555202</v>
+        <v>555086</v>
       </c>
       <c r="R11" t="n">
-        <v>6955145</v>
+        <v>6955115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,17 +1677,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119532166</v>
+        <v>119532123</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,25 +1721,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555086</v>
+        <v>555202</v>
       </c>
       <c r="R12" t="n">
-        <v>6955115</v>
+        <v>6955145</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1779,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119532161</v>
+        <v>119532159</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554754</v>
+        <v>554749</v>
       </c>
       <c r="R2" t="n">
-        <v>6954897</v>
+        <v>6954871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119532159</v>
+        <v>119532161</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554749</v>
+        <v>554754</v>
       </c>
       <c r="R3" t="n">
-        <v>6954871</v>
+        <v>6954897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119532124</v>
+        <v>119532121</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555093</v>
+        <v>555245</v>
       </c>
       <c r="R4" t="n">
-        <v>6955059</v>
+        <v>6955133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119532144</v>
+        <v>119532130</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554999</v>
+        <v>555006</v>
       </c>
       <c r="R5" t="n">
-        <v>6954973</v>
+        <v>6955030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532121</v>
+        <v>119532125</v>
       </c>
       <c r="B6" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1104,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555245</v>
+        <v>555091</v>
       </c>
       <c r="R6" t="n">
-        <v>6955133</v>
+        <v>6955066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119532196</v>
+        <v>119532193</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1230,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554849</v>
+        <v>555127</v>
       </c>
       <c r="R7" t="n">
-        <v>6954924</v>
+        <v>6954926</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119532138</v>
+        <v>119532154</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,42 +1316,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555177</v>
+        <v>555124</v>
       </c>
       <c r="R8" t="n">
-        <v>6954904</v>
+        <v>6955089</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,17 +1374,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hörd</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119532184</v>
+        <v>119532138</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,34 +1422,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554889</v>
+        <v>555177</v>
       </c>
       <c r="R9" t="n">
-        <v>6954923</v>
+        <v>6954904</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1486,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hörd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119532164</v>
+        <v>119532191</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555058</v>
+        <v>555085</v>
       </c>
       <c r="R10" t="n">
-        <v>6955092</v>
+        <v>6954991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,12 +1587,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119532166</v>
+        <v>119532129</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1636,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555086</v>
+        <v>554979</v>
       </c>
       <c r="R11" t="n">
-        <v>6955115</v>
+        <v>6954955</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119532123</v>
+        <v>119532184</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555202</v>
+        <v>554889</v>
       </c>
       <c r="R12" t="n">
-        <v>6955145</v>
+        <v>6954923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,17 +1801,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119532191</v>
+        <v>119532196</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1856,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555085</v>
+        <v>554849</v>
       </c>
       <c r="R13" t="n">
-        <v>6954991</v>
+        <v>6954924</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,17 +1903,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119532125</v>
+        <v>119532144</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,46 +1951,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555091</v>
+        <v>554999</v>
       </c>
       <c r="R14" t="n">
-        <v>6955066</v>
+        <v>6954973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119532132</v>
+        <v>119532126</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2070,17 +2070,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555085</v>
+        <v>555088</v>
       </c>
       <c r="R15" t="n">
-        <v>6955111</v>
+        <v>6954890</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,17 +2127,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532157</v>
+        <v>119532166</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2184,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555203</v>
+        <v>555086</v>
       </c>
       <c r="R16" t="n">
-        <v>6954975</v>
+        <v>6955115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2229,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2246,7 +2261,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119532126</v>
+        <v>119532123</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2279,37 +2294,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555088</v>
+        <v>555202</v>
       </c>
       <c r="R17" t="n">
-        <v>6954890</v>
+        <v>6955145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,6 +2337,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119532193</v>
+        <v>119532127</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,34 +2384,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555127</v>
+        <v>555054</v>
       </c>
       <c r="R18" t="n">
-        <v>6954926</v>
+        <v>6954969</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,12 +2454,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,7 +2588,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119532129</v>
+        <v>119532124</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2612,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554979</v>
+        <v>555093</v>
       </c>
       <c r="R20" t="n">
-        <v>6954955</v>
+        <v>6955059</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,12 +2658,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2679,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119532127</v>
+        <v>119532164</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,54 +2707,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555054</v>
+        <v>555058</v>
       </c>
       <c r="R21" t="n">
-        <v>6954969</v>
+        <v>6955092</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119532130</v>
+        <v>119532157</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,25 +2809,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555006</v>
+        <v>555203</v>
       </c>
       <c r="R22" t="n">
-        <v>6955030</v>
+        <v>6954975</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,17 +2867,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2904,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119532154</v>
+        <v>119532132</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2916,25 +2911,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2944,10 +2939,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555124</v>
+        <v>555085</v>
       </c>
       <c r="R23" t="n">
-        <v>6955089</v>
+        <v>6955111</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2974,12 +2969,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -2037,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119532126</v>
+        <v>119532166</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,58 +2049,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555088</v>
+        <v>555086</v>
       </c>
       <c r="R15" t="n">
-        <v>6954890</v>
+        <v>6955115</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,12 +2107,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532166</v>
+        <v>119532126</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2151,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555086</v>
+        <v>555088</v>
       </c>
       <c r="R16" t="n">
-        <v>6955115</v>
+        <v>6954890</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3004,6 +3004,342 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124766522</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>554803</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6954857</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färsk barkfläk</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124766519</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555080</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6955037</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>rikl färska barkfläk</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124766517</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555111</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6955077</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766522</v>
+        <v>124766519</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554803</v>
+        <v>555080</v>
       </c>
       <c r="R24" t="n">
-        <v>6954857</v>
+        <v>6955037</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766519</v>
+        <v>124766517</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555080</v>
+        <v>555111</v>
       </c>
       <c r="R25" t="n">
-        <v>6955037</v>
+        <v>6955077</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766517</v>
+        <v>124766522</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555111</v>
+        <v>554803</v>
       </c>
       <c r="R26" t="n">
-        <v>6955077</v>
+        <v>6954857</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766519</v>
+        <v>124766522</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555080</v>
+        <v>554803</v>
       </c>
       <c r="R24" t="n">
-        <v>6955037</v>
+        <v>6954857</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766517</v>
+        <v>124766519</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555111</v>
+        <v>555080</v>
       </c>
       <c r="R25" t="n">
-        <v>6955077</v>
+        <v>6955037</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766522</v>
+        <v>124766517</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554803</v>
+        <v>555111</v>
       </c>
       <c r="R26" t="n">
-        <v>6954857</v>
+        <v>6955077</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766522</v>
+        <v>124766519</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554803</v>
+        <v>555080</v>
       </c>
       <c r="R24" t="n">
-        <v>6954857</v>
+        <v>6955037</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766519</v>
+        <v>124766522</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555080</v>
+        <v>554803</v>
       </c>
       <c r="R25" t="n">
-        <v>6955037</v>
+        <v>6954857</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766519</v>
+        <v>124766522</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555080</v>
+        <v>554803</v>
       </c>
       <c r="R24" t="n">
-        <v>6955037</v>
+        <v>6954857</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766522</v>
+        <v>124766519</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554803</v>
+        <v>555080</v>
       </c>
       <c r="R25" t="n">
-        <v>6954857</v>
+        <v>6955037</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766522</v>
+        <v>124766517</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554803</v>
+        <v>555111</v>
       </c>
       <c r="R24" t="n">
-        <v>6954857</v>
+        <v>6955077</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766519</v>
+        <v>124766522</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555080</v>
+        <v>554803</v>
       </c>
       <c r="R25" t="n">
-        <v>6955037</v>
+        <v>6954857</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766517</v>
+        <v>124766519</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555111</v>
+        <v>555080</v>
       </c>
       <c r="R26" t="n">
-        <v>6955077</v>
+        <v>6955037</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766517</v>
+        <v>124766519</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555111</v>
+        <v>555080</v>
       </c>
       <c r="R24" t="n">
-        <v>6955077</v>
+        <v>6955037</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766519</v>
+        <v>124766517</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555080</v>
+        <v>555111</v>
       </c>
       <c r="R26" t="n">
-        <v>6955037</v>
+        <v>6955077</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766522</v>
+        <v>124766517</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554803</v>
+        <v>555111</v>
       </c>
       <c r="R25" t="n">
-        <v>6954857</v>
+        <v>6955077</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766517</v>
+        <v>124766522</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555111</v>
+        <v>554803</v>
       </c>
       <c r="R26" t="n">
-        <v>6955077</v>
+        <v>6954857</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3006,10 +3006,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766519</v>
+        <v>124766517</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555080</v>
+        <v>555111</v>
       </c>
       <c r="R24" t="n">
-        <v>6955037</v>
+        <v>6955077</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,7 +3121,7 @@
         <v>124766522</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766517</v>
+        <v>124766519</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555111</v>
+        <v>555080</v>
       </c>
       <c r="R26" t="n">
-        <v>6955077</v>
+        <v>6955037</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3118,7 +3118,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766522</v>
+        <v>124766519</v>
       </c>
       <c r="B25" t="n">
         <v>57635</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554803</v>
+        <v>555080</v>
       </c>
       <c r="R25" t="n">
-        <v>6954857</v>
+        <v>6955037</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färsk barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124766519</v>
+        <v>124766522</v>
       </c>
       <c r="B26" t="n">
         <v>57635</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555080</v>
+        <v>554803</v>
       </c>
       <c r="R26" t="n">
-        <v>6955037</v>
+        <v>6954857</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färsk barkfläk</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3345,7 +3345,7 @@
         <v>126740357</v>
       </c>
       <c r="B27" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>126739339</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126739812</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>126739954</v>
       </c>
       <c r="B30" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>126739616</v>
       </c>
       <c r="B31" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>126740071</v>
       </c>
       <c r="B32" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>126739199</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>126739195</v>
       </c>
       <c r="B34" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>82852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R35" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B36" t="n">
-        <v>82792</v>
+        <v>80114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R36" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>126739276</v>
       </c>
       <c r="B37" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3345,7 +3345,7 @@
         <v>126740357</v>
       </c>
       <c r="B27" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>126739339</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126739812</v>
       </c>
       <c r="B29" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>126739954</v>
       </c>
       <c r="B30" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>126739616</v>
       </c>
       <c r="B31" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>126740071</v>
       </c>
       <c r="B32" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>126739199</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>126739195</v>
       </c>
       <c r="B34" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B35" t="n">
-        <v>82852</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R35" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B36" t="n">
-        <v>80114</v>
+        <v>82855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R36" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>126739276</v>
       </c>
       <c r="B37" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>82855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R35" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B36" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R36" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3345,7 +3345,7 @@
         <v>126740357</v>
       </c>
       <c r="B27" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126739812</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>126739616</v>
       </c>
       <c r="B31" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126740071</v>
+        <v>126739199</v>
       </c>
       <c r="B32" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555018</v>
+        <v>555335</v>
       </c>
       <c r="R32" t="n">
-        <v>6955024</v>
+        <v>6955233</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126739199</v>
+        <v>126740071</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,21 +3965,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555335</v>
+        <v>555018</v>
       </c>
       <c r="R33" t="n">
-        <v>6955233</v>
+        <v>6955024</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
         <v>126739195</v>
       </c>
       <c r="B34" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>126739276</v>
       </c>
       <c r="B37" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B35" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R35" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>82855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R36" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3444,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126739339</v>
+        <v>126739812</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555331</v>
+        <v>555090</v>
       </c>
       <c r="R28" t="n">
-        <v>6955170</v>
+        <v>6955093</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126739812</v>
+        <v>126739339</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>80117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555090</v>
+        <v>555331</v>
       </c>
       <c r="R29" t="n">
-        <v>6955093</v>
+        <v>6955170</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>82855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R35" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B36" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R36" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126739199</v>
+        <v>126740071</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555335</v>
+        <v>555018</v>
       </c>
       <c r="R32" t="n">
-        <v>6955233</v>
+        <v>6955024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126740071</v>
+        <v>126739199</v>
       </c>
       <c r="B33" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,21 +3965,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555018</v>
+        <v>555335</v>
       </c>
       <c r="R33" t="n">
-        <v>6955024</v>
+        <v>6955233</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3345,7 +3345,7 @@
         <v>126740357</v>
       </c>
       <c r="B27" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126739812</v>
+        <v>126739339</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555090</v>
+        <v>555331</v>
       </c>
       <c r="R28" t="n">
-        <v>6955093</v>
+        <v>6955170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126739339</v>
+        <v>126739812</v>
       </c>
       <c r="B29" t="n">
-        <v>80117</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555331</v>
+        <v>555090</v>
       </c>
       <c r="R29" t="n">
-        <v>6955170</v>
+        <v>6955093</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
         <v>126739954</v>
       </c>
       <c r="B30" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>126739616</v>
       </c>
       <c r="B31" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126740071</v>
+        <v>126739199</v>
       </c>
       <c r="B32" t="n">
-        <v>80118</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555018</v>
+        <v>555335</v>
       </c>
       <c r="R32" t="n">
-        <v>6955024</v>
+        <v>6955233</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126739199</v>
+        <v>126740071</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>80122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,21 +3965,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555335</v>
+        <v>555018</v>
       </c>
       <c r="R33" t="n">
-        <v>6955233</v>
+        <v>6955024</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
         <v>126739195</v>
       </c>
       <c r="B34" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B35" t="n">
-        <v>82855</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R35" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>82859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R36" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>126739276</v>
       </c>
       <c r="B37" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3345,7 +3345,7 @@
         <v>126740357</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>91337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>126739339</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126739812</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>126739954</v>
       </c>
       <c r="B30" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>126739616</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>91337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126739199</v>
+        <v>126740071</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>80115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555335</v>
+        <v>555018</v>
       </c>
       <c r="R32" t="n">
-        <v>6955233</v>
+        <v>6955024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126740071</v>
+        <v>126739199</v>
       </c>
       <c r="B33" t="n">
-        <v>80122</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,21 +3965,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555018</v>
+        <v>555335</v>
       </c>
       <c r="R33" t="n">
-        <v>6955024</v>
+        <v>6955233</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
         <v>126739195</v>
       </c>
       <c r="B34" t="n">
-        <v>91348</v>
+        <v>91337</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>82852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R35" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B36" t="n">
-        <v>82859</v>
+        <v>80114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R36" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>126739276</v>
       </c>
       <c r="B37" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -3345,7 +3345,7 @@
         <v>126740357</v>
       </c>
       <c r="B27" t="n">
-        <v>91337</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>126739339</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126739812</v>
       </c>
       <c r="B29" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>126739954</v>
       </c>
       <c r="B30" t="n">
-        <v>75135</v>
+        <v>75142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>126739616</v>
       </c>
       <c r="B31" t="n">
-        <v>91337</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126740071</v>
+        <v>126739199</v>
       </c>
       <c r="B32" t="n">
-        <v>80115</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555018</v>
+        <v>555335</v>
       </c>
       <c r="R32" t="n">
-        <v>6955024</v>
+        <v>6955233</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126739199</v>
+        <v>126740071</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>80122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3965,21 +3965,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555335</v>
+        <v>555018</v>
       </c>
       <c r="R33" t="n">
-        <v>6955233</v>
+        <v>6955024</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
         <v>126739195</v>
       </c>
       <c r="B34" t="n">
-        <v>91337</v>
+        <v>91348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126739252</v>
+        <v>126740085</v>
       </c>
       <c r="B35" t="n">
-        <v>82852</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555333</v>
+        <v>555018</v>
       </c>
       <c r="R35" t="n">
-        <v>6955208</v>
+        <v>6955024</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126740085</v>
+        <v>126739252</v>
       </c>
       <c r="B36" t="n">
-        <v>80114</v>
+        <v>82859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555018</v>
+        <v>555333</v>
       </c>
       <c r="R36" t="n">
-        <v>6955024</v>
+        <v>6955208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>126739276</v>
       </c>
       <c r="B37" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119532159</v>
+        <v>126739276</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554749</v>
+        <v>555340</v>
       </c>
       <c r="R2" t="n">
-        <v>6954871</v>
+        <v>6955193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,66 +756,66 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119532161</v>
+        <v>126739812</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554754</v>
+        <v>555090</v>
       </c>
       <c r="R3" t="n">
-        <v>6954897</v>
+        <v>6955093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,31 +858,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119532121</v>
+        <v>126739252</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555245</v>
+        <v>555333</v>
       </c>
       <c r="R4" t="n">
-        <v>6955133</v>
+        <v>6955208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,31 +960,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119532130</v>
+        <v>126740071</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555006</v>
+        <v>555018</v>
       </c>
       <c r="R5" t="n">
-        <v>6955030</v>
+        <v>6955024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,17 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,31 +1062,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119532125</v>
+        <v>119532121</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,46 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555091</v>
+        <v>555245</v>
       </c>
       <c r="R6" t="n">
-        <v>6955066</v>
+        <v>6955133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,19 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119532193</v>
+        <v>119532191</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1242,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555127</v>
+        <v>555085</v>
       </c>
       <c r="R7" t="n">
-        <v>6954926</v>
+        <v>6954991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119532154</v>
+        <v>119532193</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555124</v>
+        <v>555127</v>
       </c>
       <c r="R8" t="n">
-        <v>6955089</v>
+        <v>6954926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,54 +1379,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119532138</v>
+        <v>119532196</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555177</v>
+        <v>554849</v>
       </c>
       <c r="R9" t="n">
-        <v>6954904</v>
+        <v>6954924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hörd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,19 +1476,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119532191</v>
+        <v>126739199</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1553,14 +1507,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555085</v>
+        <v>555335</v>
       </c>
       <c r="R10" t="n">
-        <v>6954991</v>
+        <v>6955233</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,17 +1541,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,31 +1557,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119532129</v>
+        <v>126739954</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,34 +1589,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554979</v>
+        <v>555089</v>
       </c>
       <c r="R11" t="n">
-        <v>6954955</v>
+        <v>6955049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,17 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,31 +1659,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119532184</v>
+        <v>119532144</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554889</v>
+        <v>554999</v>
       </c>
       <c r="R12" t="n">
-        <v>6954923</v>
+        <v>6954973</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,15 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119532196</v>
+        <v>126739339</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1788,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554849</v>
+        <v>555331</v>
       </c>
       <c r="R13" t="n">
-        <v>6954924</v>
+        <v>6955170</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1842,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,31 +1858,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119532144</v>
+        <v>126740085</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,14 +1910,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Eltnäs, Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554999</v>
+        <v>555018</v>
       </c>
       <c r="R14" t="n">
-        <v>6954973</v>
+        <v>6955024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,12 +1944,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,53 +1960,53 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med naturskogskaraktär</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119532166</v>
+        <v>119532123</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555086</v>
+        <v>555202</v>
       </c>
       <c r="R15" t="n">
-        <v>6955115</v>
+        <v>6955145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,12 +2046,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,15 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119532126</v>
+        <v>119532124</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,37 +2111,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555088</v>
+        <v>555093</v>
       </c>
       <c r="R16" t="n">
-        <v>6954890</v>
+        <v>6955059</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,15 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119532123</v>
+        <v>119532125</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,17 +2213,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555202</v>
+        <v>555091</v>
       </c>
       <c r="R17" t="n">
-        <v>6955145</v>
+        <v>6955066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,11 +2268,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,15 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119532127</v>
+        <v>119532126</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,17 +2338,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555054</v>
+        <v>555088</v>
       </c>
       <c r="R18" t="n">
-        <v>6954969</v>
+        <v>6954890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,12 +2379,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,50 +2411,61 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119532169</v>
+        <v>119532127</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555235</v>
+        <v>555054</v>
       </c>
       <c r="R19" t="n">
-        <v>6955179</v>
+        <v>6954969</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,15 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119532124</v>
+        <v>119532129</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555093</v>
+        <v>554979</v>
       </c>
       <c r="R20" t="n">
-        <v>6955059</v>
+        <v>6954955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,12 +2589,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2695,37 +2626,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119532164</v>
+        <v>119532130</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555058</v>
+        <v>555006</v>
       </c>
       <c r="R21" t="n">
-        <v>6955092</v>
+        <v>6955030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,6 +2697,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,37 +2728,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119532157</v>
+        <v>119532132</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2837,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555203</v>
+        <v>555085</v>
       </c>
       <c r="R22" t="n">
-        <v>6954975</v>
+        <v>6955111</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,12 +2793,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,15 +2830,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119532132</v>
+        <v>124766517</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,19 +2859,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555085</v>
+        <v>555111</v>
       </c>
       <c r="R23" t="n">
-        <v>6955111</v>
+        <v>6955077</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2969,17 +2900,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,27 +2925,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124766517</v>
+        <v>124766519</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555111</v>
+        <v>555080</v>
       </c>
       <c r="R24" t="n">
-        <v>6955077</v>
+        <v>6955037</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3017,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>rikl färska barkfläk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,15 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124766519</v>
+        <v>124766520</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3163,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555080</v>
+        <v>554941</v>
       </c>
       <c r="R25" t="n">
-        <v>6955037</v>
+        <v>6954892</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3203,7 +3124,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikl färska barkfläk</t>
+          <t>färska barkfläck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,12 +3154,7 @@
         <v>124766522</v>
       </c>
       <c r="B26" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,10 +3258,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126740357</v>
+        <v>119532138</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,34 +3269,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555002</v>
+        <v>555177</v>
       </c>
       <c r="R27" t="n">
-        <v>6954992</v>
+        <v>6954904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,12 +3327,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hörd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,66 +3348,61 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126739339</v>
+        <v>119532154</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555331</v>
+        <v>555124</v>
       </c>
       <c r="R28" t="n">
-        <v>6955170</v>
+        <v>6955089</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,12 +3429,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3525,66 +3445,61 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126739812</v>
+        <v>119532157</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555090</v>
+        <v>555203</v>
       </c>
       <c r="R29" t="n">
-        <v>6955093</v>
+        <v>6954975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,12 +3526,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3627,66 +3542,61 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126739954</v>
+        <v>119532159</v>
       </c>
       <c r="B30" t="n">
-        <v>75142</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555089</v>
+        <v>554749</v>
       </c>
       <c r="R30" t="n">
-        <v>6955049</v>
+        <v>6954871</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,12 +3623,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,66 +3639,61 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126739616</v>
+        <v>119532161</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555217</v>
+        <v>554754</v>
       </c>
       <c r="R31" t="n">
-        <v>6955125</v>
+        <v>6954897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3815,12 +3720,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3831,66 +3736,61 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126739199</v>
+        <v>119532164</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555335</v>
+        <v>555058</v>
       </c>
       <c r="R32" t="n">
-        <v>6955233</v>
+        <v>6955092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3917,12 +3817,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3933,66 +3833,61 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126740071</v>
+        <v>119532166</v>
       </c>
       <c r="B33" t="n">
-        <v>80122</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555018</v>
+        <v>555086</v>
       </c>
       <c r="R33" t="n">
-        <v>6955024</v>
+        <v>6955115</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4019,12 +3914,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4035,66 +3930,61 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126739195</v>
+        <v>119532169</v>
       </c>
       <c r="B34" t="n">
-        <v>91348</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555335</v>
+        <v>555235</v>
       </c>
       <c r="R34" t="n">
-        <v>6955233</v>
+        <v>6955179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,12 +4011,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4137,330 +4027,19 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>126740085</v>
-      </c>
-      <c r="B35" t="n">
-        <v>80121</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>555018</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6955024</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>126739252</v>
-      </c>
-      <c r="B36" t="n">
-        <v>82859</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>555333</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6955208</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>126739276</v>
-      </c>
-      <c r="B37" t="n">
-        <v>91330</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Eltnäs, Eltnäs, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>555340</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6955193</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med naturskogskaraktär</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31469-2024 artfynd.xlsx
+++ b/artfynd/A 31469-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739276</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739812</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739252</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126740071</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532121</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532191</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532193</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532196</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739199</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739954</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532144</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126739339</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126740085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2080,6 +2150,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532123</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532124</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,6 +2371,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532125</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2408,6 +2493,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532126</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2521,6 +2611,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532127</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532129</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532130</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2827,6 +2932,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532132</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2934,6 +3044,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766517</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766519</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3148,6 +3268,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766520</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3255,6 +3380,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766522</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3361,6 +3491,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532138</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3458,6 +3593,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532154</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3555,6 +3695,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532157</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3652,6 +3797,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532159</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3749,6 +3899,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532161</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3846,6 +4001,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532164</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3943,6 +4103,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532166</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4040,8 +4205,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119532169</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>